--- a/12600512.xlsx
+++ b/12600512.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -177,6 +177,12 @@
   </si>
   <si>
     <t>Good day</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>Medium</t>
   </si>
 </sst>
 </file>
@@ -933,24 +939,48 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="16"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
+      <c r="A7" s="16">
+        <v>46252</v>
+      </c>
+      <c r="B7" s="17">
+        <v>300</v>
+      </c>
+      <c r="C7" s="17">
+        <v>60</v>
+      </c>
+      <c r="D7" s="17">
+        <v>300</v>
+      </c>
+      <c r="E7" s="17">
+        <v>300</v>
+      </c>
+      <c r="F7" s="17">
+        <v>300</v>
+      </c>
+      <c r="G7" s="17">
+        <v>4</v>
+      </c>
+      <c r="H7" s="17">
+        <v>60</v>
+      </c>
       <c r="I7" s="18">
         <f t="shared" si="0"/>
       </c>
       <c r="J7" s="18">
         <f t="shared" si="1"/>
       </c>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="20"/>
+      <c r="K7" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="L7" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="M7" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="N7" s="20" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>

--- a/12600512.xlsx
+++ b/12600512.xlsx
@@ -952,7 +952,7 @@
         <v>300</v>
       </c>
       <c r="E7" s="17">
-        <v>300</v>
+        <v>390</v>
       </c>
       <c r="F7" s="17">
         <v>300</v>

--- a/12600512.xlsx
+++ b/12600512.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="57">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -170,7 +170,7 @@
     <t>Excellent</t>
   </si>
   <si>
-    <t>Very Satisfied</t>
+    <t>Neutral</t>
   </si>
   <si>
     <t>High</t>
@@ -180,6 +180,9 @@
   </si>
   <si>
     <t>Good</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
   </si>
   <si>
     <t>Medium</t>
@@ -903,7 +906,7 @@
         <v>60</v>
       </c>
       <c r="D6" s="12">
-        <v>420</v>
+        <v>120</v>
       </c>
       <c r="E6" s="12">
         <v>300</v>
@@ -973,10 +976,10 @@
         <v>54</v>
       </c>
       <c r="L7" s="19" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="M7" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N7" s="20" t="s">
         <v>53</v>

--- a/12600512.xlsx
+++ b/12600512.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="57">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -986,24 +986,48 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="16"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
+      <c r="A8" s="16">
+        <v>46250</v>
+      </c>
+      <c r="B8" s="17">
+        <v>300</v>
+      </c>
+      <c r="C8" s="17">
+        <v>60</v>
+      </c>
+      <c r="D8" s="17">
+        <v>300</v>
+      </c>
+      <c r="E8" s="17">
+        <v>390</v>
+      </c>
+      <c r="F8" s="17">
+        <v>300</v>
+      </c>
+      <c r="G8" s="17">
+        <v>4</v>
+      </c>
+      <c r="H8" s="17">
+        <v>60</v>
+      </c>
       <c r="I8" s="18">
         <f t="shared" si="0"/>
       </c>
       <c r="J8" s="18">
         <f t="shared" si="1"/>
       </c>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="20"/>
+      <c r="K8" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="L8" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="M8" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="N8" s="20" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="16"/>

--- a/12600512.xlsx
+++ b/12600512.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="58">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -186,6 +186,9 @@
   </si>
   <si>
     <t>Medium</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
   </si>
 </sst>
 </file>
@@ -1030,24 +1033,48 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="16"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
+      <c r="A9" s="16">
+        <v>46253</v>
+      </c>
+      <c r="B9" s="17">
+        <v>300</v>
+      </c>
+      <c r="C9" s="17">
+        <v>60</v>
+      </c>
+      <c r="D9" s="17">
+        <v>300</v>
+      </c>
+      <c r="E9" s="17">
+        <v>390</v>
+      </c>
+      <c r="F9" s="17">
+        <v>300</v>
+      </c>
+      <c r="G9" s="17">
+        <v>4</v>
+      </c>
+      <c r="H9" s="17">
+        <v>60</v>
+      </c>
       <c r="I9" s="18">
         <f t="shared" si="0"/>
       </c>
       <c r="J9" s="18">
         <f t="shared" si="1"/>
       </c>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="20"/>
+      <c r="K9" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="L9" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="M9" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="N9" s="20" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
